--- a/frontend/playwright/fixtures/fluorocycler-e2e-results-demo.xlsx
+++ b/frontend/playwright/fixtures/fluorocycler-e2e-results-demo.xlsx
@@ -433,7 +433,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>DEMO-FC-2026-00001</v>
+        <v>DEV01263000000000101</v>
       </c>
       <c r="B2" t="str">
         <v>A1</v>
@@ -465,7 +465,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>DEMO-FC-2026-00001</v>
+        <v>DEV01263000000000101</v>
       </c>
       <c r="B3" t="str">
         <v>A1</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>DEMO-FC-2026-00002</v>
+        <v>DEV01263000000000102</v>
       </c>
       <c r="B4" t="str">
         <v>B1</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>DEMO-FC-2026-00002</v>
+        <v>DEV01263000000000102</v>
       </c>
       <c r="B5" t="str">
         <v>B1</v>
@@ -549,7 +549,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>DEMO-FC-2026-00003</v>
+        <v>DEV01263000000000103</v>
       </c>
       <c r="B6" t="str">
         <v>C1</v>
@@ -572,7 +572,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>DEMO-FC-2026-00003</v>
+        <v>DEV01263000000000103</v>
       </c>
       <c r="B7" t="str">
         <v>C1</v>
